--- a/protypo-tameia.xlsx
+++ b/protypo-tameia.xlsx
@@ -14851,7 +14851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X200"/>
+  <dimension ref="A1:Y200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14876,7 +14876,8 @@
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
     <col width="24" customWidth="1" min="22" max="22"/>
-    <col width="60" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="60" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -14990,7 +14991,12 @@
           <t>Σημειώσεις</t>
         </is>
       </c>
-      <c r="X1" s="5" t="inlineStr">
+      <c r="W1" s="4" t="inlineStr">
+        <is>
+          <t>Ανήκει στο διαμέρισμα</t>
+        </is>
+      </c>
+      <c r="Y1" s="5" t="inlineStr">
         <is>
           <t>Διαμερίσματα (για τα κοινόχρηστα)</t>
         </is>
@@ -15064,7 +15070,7 @@
           <t>Ενοικιαστής</t>
         </is>
       </c>
-      <c r="X2" s="9" t="inlineStr">
+      <c r="Y2" s="9" t="inlineStr">
         <is>
           <t>Απαραίτητο μόνο το «Διαμέρισμα» (π.χ. Α1).</t>
         </is>
@@ -15073,7 +15079,7 @@
     <row r="3">
       <c r="M3" s="10" t="n"/>
       <c r="N3" s="10" t="n"/>
-      <c r="X3" s="9" t="inlineStr">
+      <c r="Y3" s="9" t="inlineStr">
         <is>
           <t>Χιλιοστά: από τον πίνακα χιλιοστών. Ενοικιάζεται: «Ναι» αν έχει ενοικιαστή.</t>
         </is>
@@ -15082,7 +15088,7 @@
     <row r="4">
       <c r="M4" s="10" t="n"/>
       <c r="N4" s="10" t="n"/>
-      <c r="X4" s="9" t="inlineStr">
+      <c r="Y4" s="9" t="inlineStr">
         <is>
           <t>Πληρώνει: Ενοικιαστής ή Ιδιοκτήτης (ποιος πληρώνει τα κοινόχρηστα).</t>
         </is>
@@ -15091,7 +15097,7 @@
     <row r="5">
       <c r="M5" s="10" t="n"/>
       <c r="N5" s="10" t="n"/>
-      <c r="X5" s="9" t="inlineStr">
+      <c r="Y5" s="9" t="inlineStr">
         <is>
           <t>ει, fi: συντελεστές ωρομετρητών από τη μελέτη (αν υπάρχουν).</t>
         </is>
@@ -15100,6 +15106,11 @@
     <row r="6">
       <c r="M6" s="10" t="n"/>
       <c r="N6" s="10" t="n"/>
+      <c r="Y6" s="9" t="inlineStr">
+        <is>
+          <t>Ανήκει στο διαμέρισμα: για θέση στάθμευσης ή αποθήκη — τα χιλιοστά της προστίθενται στο διαμέρισμα αυτό.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="M7" s="10" t="n"/>
